--- a/instance/Fokashchuk/data_modified.xlsx
+++ b/instance/Fokashchuk/data_modified.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\em27upeq\PycharmProjects\RCxn\instance\Fokashchuk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F7A0DF-4DB9-4A4E-8AB6-71336578127F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20FA618-2E75-411A-8787-BD06DD255641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/instance/Fokashchuk/data_modified.xlsx
+++ b/instance/Fokashchuk/data_modified.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\em27upeq\PycharmProjects\RCxn\instance\Fokashchuk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04A61AD-1A55-485C-AFBE-62A2922E25A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE48C38-FA25-4D32-BE54-56EE4F821A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="237">
   <si>
     <t>ID</t>
   </si>
@@ -728,6 +728,15 @@
   <si>
     <t>Kontsentratsiia na + LOC.</t>
   </si>
+  <si>
+    <t>Hinweis</t>
+  </si>
+  <si>
+    <t>Satire</t>
+  </si>
+  <si>
+    <t>Ausblick</t>
+  </si>
 </sst>
 </file>
 
@@ -2362,7 +2371,9 @@
       <c r="F12" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>234</v>
+      </c>
       <c r="H12" s="5" t="s">
         <v>37</v>
       </c>
@@ -2485,7 +2496,9 @@
       <c r="F13" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="6" t="s">
+        <v>235</v>
+      </c>
       <c r="H13" s="5" t="s">
         <v>37</v>
       </c>
@@ -2608,7 +2621,9 @@
       <c r="F14" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>236</v>
+      </c>
       <c r="H14" s="5" t="s">
         <v>37</v>
       </c>
@@ -2793,7 +2808,9 @@
         <v>41</v>
       </c>
       <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -2909,7 +2926,9 @@
         <v>211</v>
       </c>
       <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="N18" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
@@ -30323,5 +30342,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>